--- a/Team-Data/2007-08/11-29-2007-08.xlsx
+++ b/Team-Data/2007-08/11-29-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,22 +806,22 @@
         <v>-1.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE2" t="n">
         <v>19</v>
       </c>
       <c r="AF2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG2" t="n">
         <v>20</v>
       </c>
       <c r="AH2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AI2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ2" t="n">
         <v>25</v>
@@ -769,10 +836,10 @@
         <v>28</v>
       </c>
       <c r="AN2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP2" t="n">
         <v>13</v>
@@ -811,7 +878,7 @@
         <v>14</v>
       </c>
       <c r="BB2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC2" t="n">
         <v>16</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>11-29-2007-08</t>
+          <t>2007-11-29</t>
         </is>
       </c>
     </row>
@@ -843,85 +910,85 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.857</v>
+        <v>0.846</v>
       </c>
       <c r="H3" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="I3" t="n">
         <v>37.4</v>
       </c>
       <c r="J3" t="n">
-        <v>76.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="K3" t="n">
-        <v>0.489</v>
+        <v>0.49</v>
       </c>
       <c r="L3" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="M3" t="n">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="N3" t="n">
-        <v>0.395</v>
+        <v>0.381</v>
       </c>
       <c r="O3" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="P3" t="n">
-        <v>27.6</v>
+        <v>27.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.752</v>
+        <v>0.754</v>
       </c>
       <c r="R3" t="n">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>33.9</v>
+        <v>33.4</v>
       </c>
       <c r="T3" t="n">
-        <v>42.7</v>
+        <v>42.1</v>
       </c>
       <c r="U3" t="n">
-        <v>24.7</v>
+        <v>24.5</v>
       </c>
       <c r="V3" t="n">
-        <v>15.9</v>
+        <v>16.5</v>
       </c>
       <c r="W3" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y3" t="n">
         <v>5.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="AB3" t="n">
-        <v>102.9</v>
+        <v>102.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>14</v>
+        <v>11.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AE3" t="n">
         <v>3</v>
@@ -936,7 +1003,7 @@
         <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AJ3" t="n">
         <v>28</v>
@@ -945,7 +1012,7 @@
         <v>2</v>
       </c>
       <c r="AL3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AM3" t="n">
         <v>13</v>
@@ -957,7 +1024,7 @@
         <v>11</v>
       </c>
       <c r="AP3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ3" t="n">
         <v>14</v>
@@ -966,22 +1033,22 @@
         <v>29</v>
       </c>
       <c r="AS3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU3" t="n">
         <v>3</v>
       </c>
       <c r="AV3" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AW3" t="n">
         <v>3</v>
       </c>
       <c r="AX3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AY3" t="n">
         <v>19</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>11-29-2007-08</t>
+          <t>2007-11-29</t>
         </is>
       </c>
     </row>
@@ -1103,13 +1170,13 @@
         <v>-4.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE4" t="n">
         <v>19</v>
       </c>
       <c r="AF4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG4" t="n">
         <v>20</v>
@@ -1118,16 +1185,16 @@
         <v>9</v>
       </c>
       <c r="AI4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK4" t="n">
         <v>25</v>
       </c>
       <c r="AL4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM4" t="n">
         <v>18</v>
@@ -1145,10 +1212,10 @@
         <v>30</v>
       </c>
       <c r="AR4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT4" t="n">
         <v>13</v>
@@ -1169,13 +1236,13 @@
         <v>29</v>
       </c>
       <c r="AZ4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA4" t="n">
         <v>19</v>
       </c>
       <c r="BB4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC4" t="n">
         <v>22</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>11-29-2007-08</t>
+          <t>2007-11-29</t>
         </is>
       </c>
     </row>
@@ -1285,13 +1352,13 @@
         <v>-8.300000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE5" t="n">
         <v>28</v>
       </c>
       <c r="AF5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG5" t="n">
         <v>28</v>
@@ -1333,7 +1400,7 @@
         <v>19</v>
       </c>
       <c r="AT5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU5" t="n">
         <v>21</v>
@@ -1360,7 +1427,7 @@
         <v>30</v>
       </c>
       <c r="BC5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>11-29-2007-08</t>
+          <t>2007-11-29</t>
         </is>
       </c>
     </row>
@@ -1467,16 +1534,16 @@
         <v>-2.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE6" t="n">
         <v>8</v>
       </c>
       <c r="AF6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG6" t="n">
         <v>11</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>10</v>
       </c>
       <c r="AH6" t="n">
         <v>6</v>
@@ -1485,16 +1552,16 @@
         <v>10</v>
       </c>
       <c r="AJ6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK6" t="n">
         <v>16</v>
       </c>
       <c r="AL6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AN6" t="n">
         <v>8</v>
@@ -1515,7 +1582,7 @@
         <v>12</v>
       </c>
       <c r="AT6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AU6" t="n">
         <v>23</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>11-29-2007-08</t>
+          <t>2007-11-29</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>4.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE7" t="n">
         <v>6</v>
@@ -1697,7 +1764,7 @@
         <v>11</v>
       </c>
       <c r="AT7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU7" t="n">
         <v>19</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>11-29-2007-08</t>
+          <t>2007-11-29</t>
         </is>
       </c>
     </row>
@@ -1753,136 +1820,136 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E8" t="n">
         <v>9</v>
       </c>
       <c r="F8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="H8" t="n">
         <v>48</v>
       </c>
       <c r="I8" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J8" t="n">
-        <v>83.8</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K8" t="n">
         <v>0.449</v>
       </c>
       <c r="L8" t="n">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="M8" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="N8" t="n">
-        <v>0.337</v>
+        <v>0.344</v>
       </c>
       <c r="O8" t="n">
-        <v>22.9</v>
+        <v>23.5</v>
       </c>
       <c r="P8" t="n">
-        <v>30.8</v>
+        <v>31.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="R8" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="S8" t="n">
-        <v>33.3</v>
+        <v>33.7</v>
       </c>
       <c r="T8" t="n">
-        <v>44.4</v>
+        <v>44.7</v>
       </c>
       <c r="U8" t="n">
-        <v>22.7</v>
+        <v>23</v>
       </c>
       <c r="V8" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="W8" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="X8" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="Z8" t="n">
         <v>22.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>24.4</v>
+        <v>24.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>105.1</v>
+        <v>105.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.1</v>
+        <v>5.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AE8" t="n">
         <v>8</v>
       </c>
       <c r="AF8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AG8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH8" t="n">
         <v>18</v>
       </c>
       <c r="AI8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>8</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>7</v>
       </c>
       <c r="AK8" t="n">
         <v>14</v>
       </c>
       <c r="AL8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM8" t="n">
         <v>6</v>
       </c>
       <c r="AN8" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AO8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP8" t="n">
         <v>2</v>
       </c>
       <c r="AQ8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR8" t="n">
         <v>16</v>
       </c>
-      <c r="AR8" t="n">
-        <v>17</v>
-      </c>
       <c r="AS8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU8" t="n">
         <v>5</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>8</v>
       </c>
       <c r="AV8" t="n">
         <v>26</v>
@@ -1894,19 +1961,19 @@
         <v>1</v>
       </c>
       <c r="AY8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ8" t="n">
         <v>18</v>
       </c>
       <c r="BA8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC8" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>11-29-2007-08</t>
+          <t>2007-11-29</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>5.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE9" t="n">
         <v>8</v>
@@ -2031,10 +2098,10 @@
         <v>11</v>
       </c>
       <c r="AJ9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL9" t="n">
         <v>21</v>
@@ -2052,13 +2119,13 @@
         <v>18</v>
       </c>
       <c r="AQ9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR9" t="n">
         <v>15</v>
       </c>
       <c r="AS9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT9" t="n">
         <v>22</v>
@@ -2070,7 +2137,7 @@
         <v>3</v>
       </c>
       <c r="AW9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX9" t="n">
         <v>7</v>
@@ -2088,7 +2155,7 @@
         <v>17</v>
       </c>
       <c r="BC9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>11-29-2007-08</t>
+          <t>2007-11-29</t>
         </is>
       </c>
     </row>
@@ -2117,97 +2184,97 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F10" t="n">
         <v>7</v>
       </c>
       <c r="G10" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="H10" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I10" t="n">
         <v>40.3</v>
       </c>
       <c r="J10" t="n">
-        <v>88.2</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.457</v>
+        <v>0.453</v>
       </c>
       <c r="L10" t="n">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>26.5</v>
+        <v>27.1</v>
       </c>
       <c r="N10" t="n">
-        <v>0.345</v>
+        <v>0.343</v>
       </c>
       <c r="O10" t="n">
-        <v>18.8</v>
+        <v>18.4</v>
       </c>
       <c r="P10" t="n">
-        <v>27.3</v>
+        <v>26.8</v>
       </c>
       <c r="Q10" t="n">
         <v>0.6879999999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
       <c r="S10" t="n">
-        <v>29.7</v>
+        <v>29.3</v>
       </c>
       <c r="T10" t="n">
-        <v>41.8</v>
+        <v>41.6</v>
       </c>
       <c r="U10" t="n">
         <v>22.1</v>
       </c>
       <c r="V10" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="W10" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="X10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>108.6</v>
+        <v>108.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.7</v>
+        <v>-0.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AE10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AF10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AH10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI10" t="n">
         <v>2</v>
@@ -2216,7 +2283,7 @@
         <v>1</v>
       </c>
       <c r="AK10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL10" t="n">
         <v>1</v>
@@ -2225,22 +2292,22 @@
         <v>1</v>
       </c>
       <c r="AN10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AO10" t="n">
         <v>16</v>
       </c>
       <c r="AP10" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AQ10" t="n">
         <v>28</v>
       </c>
       <c r="AR10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AS10" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AT10" t="n">
         <v>19</v>
@@ -2255,13 +2322,13 @@
         <v>6</v>
       </c>
       <c r="AX10" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AY10" t="n">
         <v>20</v>
       </c>
       <c r="AZ10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BA10" t="n">
         <v>8</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>11-29-2007-08</t>
+          <t>2007-11-29</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E11" t="n">
         <v>9</v>
       </c>
       <c r="F11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G11" t="n">
-        <v>0.529</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H11" t="n">
         <v>48</v>
@@ -2323,70 +2390,70 @@
         <v>0.441</v>
       </c>
       <c r="L11" t="n">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="M11" t="n">
-        <v>19.4</v>
+        <v>19.7</v>
       </c>
       <c r="N11" t="n">
-        <v>0.312</v>
+        <v>0.317</v>
       </c>
       <c r="O11" t="n">
         <v>16.4</v>
       </c>
       <c r="P11" t="n">
-        <v>22.7</v>
+        <v>22.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.723</v>
+        <v>0.736</v>
       </c>
       <c r="R11" t="n">
         <v>12.6</v>
       </c>
       <c r="S11" t="n">
-        <v>31.9</v>
+        <v>32.1</v>
       </c>
       <c r="T11" t="n">
-        <v>44.5</v>
+        <v>44.7</v>
       </c>
       <c r="U11" t="n">
-        <v>20.9</v>
+        <v>20.6</v>
       </c>
       <c r="V11" t="n">
         <v>14.5</v>
       </c>
       <c r="W11" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="X11" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z11" t="n">
-        <v>21.4</v>
+        <v>21.1</v>
       </c>
       <c r="AA11" t="n">
         <v>20.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>95.3</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD11" t="n">
         <v>2</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
       </c>
       <c r="AF11" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AG11" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AH11" t="n">
         <v>18</v>
@@ -2401,13 +2468,13 @@
         <v>22</v>
       </c>
       <c r="AL11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AM11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AN11" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AO11" t="n">
         <v>24</v>
@@ -2416,16 +2483,16 @@
         <v>23</v>
       </c>
       <c r="AQ11" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AR11" t="n">
         <v>9</v>
       </c>
       <c r="AS11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU11" t="n">
         <v>15</v>
@@ -2434,25 +2501,25 @@
         <v>8</v>
       </c>
       <c r="AW11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX11" t="n">
         <v>17</v>
       </c>
       <c r="AY11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AZ11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA11" t="n">
         <v>22</v>
       </c>
       <c r="BB11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>11-29-2007-08</t>
+          <t>2007-11-29</t>
         </is>
       </c>
     </row>
@@ -2559,22 +2626,22 @@
         <v>-1.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH12" t="n">
         <v>15</v>
       </c>
       <c r="AI12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ12" t="n">
         <v>4</v>
@@ -2589,13 +2656,13 @@
         <v>4</v>
       </c>
       <c r="AN12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO12" t="n">
         <v>13</v>
       </c>
       <c r="AP12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ12" t="n">
         <v>17</v>
@@ -2604,16 +2671,16 @@
         <v>8</v>
       </c>
       <c r="AS12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT12" t="n">
         <v>1</v>
       </c>
       <c r="AU12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW12" t="n">
         <v>15</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>11-29-2007-08</t>
+          <t>2007-11-29</t>
         </is>
       </c>
     </row>
@@ -2741,13 +2808,13 @@
         <v>-4.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE13" t="n">
         <v>19</v>
       </c>
       <c r="AF13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG13" t="n">
         <v>19</v>
@@ -2759,13 +2826,13 @@
         <v>29</v>
       </c>
       <c r="AJ13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK13" t="n">
         <v>29</v>
       </c>
       <c r="AL13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM13" t="n">
         <v>19</v>
@@ -2789,7 +2856,7 @@
         <v>6</v>
       </c>
       <c r="AT13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU13" t="n">
         <v>21</v>
@@ -2813,7 +2880,7 @@
         <v>17</v>
       </c>
       <c r="BB13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC13" t="n">
         <v>23</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>11-29-2007-08</t>
+          <t>2007-11-29</t>
         </is>
       </c>
     </row>
@@ -2845,106 +2912,106 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F14" t="n">
         <v>6</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6</v>
+        <v>0.571</v>
       </c>
       <c r="H14" t="n">
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>37.8</v>
+        <v>37.1</v>
       </c>
       <c r="J14" t="n">
-        <v>80.40000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.47</v>
+        <v>0.467</v>
       </c>
       <c r="L14" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M14" t="n">
-        <v>18.7</v>
+        <v>18.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0.359</v>
+        <v>0.355</v>
       </c>
       <c r="O14" t="n">
-        <v>24.3</v>
+        <v>24.5</v>
       </c>
       <c r="P14" t="n">
         <v>31.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.778</v>
+        <v>0.783</v>
       </c>
       <c r="R14" t="n">
-        <v>11.1</v>
+        <v>10.7</v>
       </c>
       <c r="S14" t="n">
-        <v>34.1</v>
+        <v>34</v>
       </c>
       <c r="T14" t="n">
-        <v>45.2</v>
+        <v>44.7</v>
       </c>
       <c r="U14" t="n">
-        <v>22.8</v>
+        <v>22.1</v>
       </c>
       <c r="V14" t="n">
         <v>16.3</v>
       </c>
       <c r="W14" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="X14" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>106.7</v>
+        <v>105.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AE14" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AF14" t="n">
         <v>8</v>
       </c>
       <c r="AG14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH14" t="n">
         <v>18</v>
       </c>
       <c r="AI14" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AJ14" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AK14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AL14" t="n">
         <v>12</v>
@@ -2953,7 +3020,7 @@
         <v>12</v>
       </c>
       <c r="AN14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AO14" t="n">
         <v>1</v>
@@ -2962,10 +3029,10 @@
         <v>1</v>
       </c>
       <c r="AQ14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AR14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS14" t="n">
         <v>2</v>
@@ -2974,19 +3041,19 @@
         <v>2</v>
       </c>
       <c r="AU14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AV14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX14" t="n">
         <v>23</v>
       </c>
-      <c r="AW14" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>24</v>
-      </c>
       <c r="AY14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ14" t="n">
         <v>16</v>
@@ -2995,10 +3062,10 @@
         <v>7</v>
       </c>
       <c r="BB14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BC14" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>11-29-2007-08</t>
+          <t>2007-11-29</t>
         </is>
       </c>
     </row>
@@ -3105,25 +3172,25 @@
         <v>-3</v>
       </c>
       <c r="AD15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE15" t="n">
         <v>22</v>
       </c>
       <c r="AF15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG15" t="n">
         <v>22</v>
       </c>
       <c r="AH15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK15" t="n">
         <v>9</v>
@@ -3165,7 +3232,7 @@
         <v>30</v>
       </c>
       <c r="AX15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY15" t="n">
         <v>14</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>11-29-2007-08</t>
+          <t>2007-11-29</t>
         </is>
       </c>
     </row>
@@ -3287,16 +3354,16 @@
         <v>-3.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE16" t="n">
         <v>25</v>
       </c>
       <c r="AF16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH16" t="n">
         <v>18</v>
@@ -3317,7 +3384,7 @@
         <v>26</v>
       </c>
       <c r="AN16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO16" t="n">
         <v>23</v>
@@ -3332,7 +3399,7 @@
         <v>30</v>
       </c>
       <c r="AS16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT16" t="n">
         <v>30</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>11-29-2007-08</t>
+          <t>2007-11-29</t>
         </is>
       </c>
     </row>
@@ -3469,16 +3536,16 @@
         <v>-2.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF17" t="n">
         <v>8</v>
       </c>
       <c r="AG17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH17" t="n">
         <v>18</v>
@@ -3487,7 +3554,7 @@
         <v>16</v>
       </c>
       <c r="AJ17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK17" t="n">
         <v>10</v>
@@ -3508,13 +3575,13 @@
         <v>21</v>
       </c>
       <c r="AQ17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT17" t="n">
         <v>16</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>11-29-2007-08</t>
+          <t>2007-11-29</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-7</v>
       </c>
       <c r="AD18" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE18" t="n">
         <v>29</v>
@@ -3669,7 +3736,7 @@
         <v>17</v>
       </c>
       <c r="AJ18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK18" t="n">
         <v>13</v>
@@ -3693,7 +3760,7 @@
         <v>22</v>
       </c>
       <c r="AR18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS18" t="n">
         <v>29</v>
@@ -3705,13 +3772,13 @@
         <v>26</v>
       </c>
       <c r="AV18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW18" t="n">
         <v>10</v>
       </c>
       <c r="AX18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY18" t="n">
         <v>10</v>
@@ -3723,10 +3790,10 @@
         <v>28</v>
       </c>
       <c r="BB18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>11-29-2007-08</t>
+          <t>2007-11-29</t>
         </is>
       </c>
     </row>
@@ -3833,19 +3900,19 @@
         <v>-6.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG19" t="n">
         <v>17</v>
       </c>
       <c r="AH19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI19" t="n">
         <v>30</v>
@@ -3863,7 +3930,7 @@
         <v>14</v>
       </c>
       <c r="AN19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO19" t="n">
         <v>8</v>
@@ -3872,7 +3939,7 @@
         <v>6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR19" t="n">
         <v>22</v>
@@ -3902,13 +3969,13 @@
         <v>28</v>
       </c>
       <c r="BA19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB19" t="n">
         <v>28</v>
       </c>
       <c r="BC19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>11-29-2007-08</t>
+          <t>2007-11-29</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>3.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE20" t="n">
         <v>6</v>
@@ -4090,7 +4157,7 @@
         <v>19</v>
       </c>
       <c r="BC20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>11-29-2007-08</t>
+          <t>2007-11-29</t>
         </is>
       </c>
     </row>
@@ -4119,85 +4186,85 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E21" t="n">
         <v>4</v>
       </c>
       <c r="F21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G21" t="n">
-        <v>0.286</v>
+        <v>0.308</v>
       </c>
       <c r="H21" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="I21" t="n">
-        <v>34.6</v>
+        <v>35.5</v>
       </c>
       <c r="J21" t="n">
-        <v>81.2</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.426</v>
+        <v>0.434</v>
       </c>
       <c r="L21" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="M21" t="n">
-        <v>15.1</v>
+        <v>15.5</v>
       </c>
       <c r="N21" t="n">
-        <v>0.318</v>
+        <v>0.323</v>
       </c>
       <c r="O21" t="n">
-        <v>19.3</v>
+        <v>19.9</v>
       </c>
       <c r="P21" t="n">
-        <v>27.1</v>
+        <v>27.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.711</v>
+        <v>0.713</v>
       </c>
       <c r="R21" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="S21" t="n">
-        <v>30.9</v>
+        <v>31.1</v>
       </c>
       <c r="T21" t="n">
-        <v>43.9</v>
+        <v>44.5</v>
       </c>
       <c r="U21" t="n">
-        <v>17.2</v>
+        <v>17.6</v>
       </c>
       <c r="V21" t="n">
-        <v>17.1</v>
+        <v>17.3</v>
       </c>
       <c r="W21" t="n">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="X21" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Y21" t="n">
         <v>6.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="AB21" t="n">
-        <v>93.2</v>
+        <v>95.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>-9.199999999999999</v>
+        <v>-6.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AE21" t="n">
         <v>25</v>
@@ -4212,40 +4279,40 @@
         <v>1</v>
       </c>
       <c r="AI21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK21" t="n">
         <v>26</v>
       </c>
-      <c r="AJ21" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>27</v>
-      </c>
       <c r="AL21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM21" t="n">
         <v>24</v>
       </c>
       <c r="AN21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO21" t="n">
         <v>14</v>
       </c>
       <c r="AP21" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AQ21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT21" t="n">
         <v>5</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>17</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>11</v>
       </c>
       <c r="AU21" t="n">
         <v>29</v>
@@ -4254,25 +4321,25 @@
         <v>29</v>
       </c>
       <c r="AW21" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
       </c>
       <c r="AY21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AZ21" t="n">
         <v>23</v>
       </c>
       <c r="BA21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB21" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="BC21" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>11-29-2007-08</t>
+          <t>2007-11-29</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4467,7 @@
         <v>26</v>
       </c>
       <c r="AK22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL22" t="n">
         <v>2</v>
@@ -4409,7 +4476,7 @@
         <v>2</v>
       </c>
       <c r="AN22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO22" t="n">
         <v>10</v>
@@ -4427,7 +4494,7 @@
         <v>1</v>
       </c>
       <c r="AT22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU22" t="n">
         <v>13</v>
@@ -4439,7 +4506,7 @@
         <v>29</v>
       </c>
       <c r="AX22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY22" t="n">
         <v>3</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>11-29-2007-08</t>
+          <t>2007-11-29</t>
         </is>
       </c>
     </row>
@@ -4561,25 +4628,25 @@
         <v>-3.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE23" t="n">
         <v>25</v>
       </c>
       <c r="AF23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH23" t="n">
         <v>9</v>
       </c>
       <c r="AI23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK23" t="n">
         <v>23</v>
@@ -4618,7 +4685,7 @@
         <v>25</v>
       </c>
       <c r="AW23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX23" t="n">
         <v>9</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>11-29-2007-08</t>
+          <t>2007-11-29</t>
         </is>
       </c>
     </row>
@@ -4743,10 +4810,10 @@
         <v>5.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF24" t="n">
         <v>4</v>
@@ -4782,7 +4849,7 @@
         <v>24</v>
       </c>
       <c r="AQ24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR24" t="n">
         <v>28</v>
@@ -4818,7 +4885,7 @@
         <v>2</v>
       </c>
       <c r="BC24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>11-29-2007-08</t>
+          <t>2007-11-29</t>
         </is>
       </c>
     </row>
@@ -4925,13 +4992,13 @@
         <v>-4.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE25" t="n">
         <v>22</v>
       </c>
       <c r="AF25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG25" t="n">
         <v>22</v>
@@ -4940,13 +5007,13 @@
         <v>18</v>
       </c>
       <c r="AI25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ25" t="n">
         <v>27</v>
       </c>
       <c r="AK25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL25" t="n">
         <v>19</v>
@@ -4955,7 +5022,7 @@
         <v>21</v>
       </c>
       <c r="AN25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO25" t="n">
         <v>25</v>
@@ -4964,7 +5031,7 @@
         <v>24</v>
       </c>
       <c r="AQ25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR25" t="n">
         <v>25</v>
@@ -4979,7 +5046,7 @@
         <v>16</v>
       </c>
       <c r="AV25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW25" t="n">
         <v>26</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>11-29-2007-08</t>
+          <t>2007-11-29</t>
         </is>
       </c>
     </row>
@@ -5107,13 +5174,13 @@
         <v>-4.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE26" t="n">
         <v>22</v>
       </c>
       <c r="AF26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG26" t="n">
         <v>22</v>
@@ -5122,7 +5189,7 @@
         <v>4</v>
       </c>
       <c r="AI26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ26" t="n">
         <v>24</v>
@@ -5137,7 +5204,7 @@
         <v>23</v>
       </c>
       <c r="AN26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO26" t="n">
         <v>2</v>
@@ -5152,7 +5219,7 @@
         <v>23</v>
       </c>
       <c r="AS26" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT26" t="n">
         <v>28</v>
@@ -5161,7 +5228,7 @@
         <v>30</v>
       </c>
       <c r="AV26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW26" t="n">
         <v>18</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>11-29-2007-08</t>
+          <t>2007-11-29</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>8.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE27" t="n">
         <v>2</v>
@@ -5307,7 +5374,7 @@
         <v>4</v>
       </c>
       <c r="AJ27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK27" t="n">
         <v>4</v>
@@ -5340,7 +5407,7 @@
         <v>26</v>
       </c>
       <c r="AU27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV27" t="n">
         <v>1</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>11-29-2007-08</t>
+          <t>2007-11-29</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="AD28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE28" t="n">
         <v>29</v>
@@ -5486,13 +5553,13 @@
         <v>6</v>
       </c>
       <c r="AI28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ28" t="n">
         <v>2</v>
       </c>
       <c r="AK28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL28" t="n">
         <v>26</v>
@@ -5516,28 +5583,28 @@
         <v>13</v>
       </c>
       <c r="AS28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU28" t="n">
         <v>20</v>
       </c>
       <c r="AV28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW28" t="n">
         <v>13</v>
       </c>
       <c r="AX28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY28" t="n">
         <v>18</v>
       </c>
       <c r="AZ28" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA28" t="n">
         <v>21</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>11-29-2007-08</t>
+          <t>2007-11-29</t>
         </is>
       </c>
     </row>
@@ -5653,22 +5720,22 @@
         <v>4.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ29" t="n">
         <v>6</v>
@@ -5698,7 +5765,7 @@
         <v>21</v>
       </c>
       <c r="AS29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT29" t="n">
         <v>23</v>
@@ -5710,7 +5777,7 @@
         <v>2</v>
       </c>
       <c r="AW29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX29" t="n">
         <v>25</v>
@@ -5719,7 +5786,7 @@
         <v>17</v>
       </c>
       <c r="AZ29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA29" t="n">
         <v>30</v>
@@ -5728,7 +5795,7 @@
         <v>15</v>
       </c>
       <c r="BC29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>11-29-2007-08</t>
+          <t>2007-11-29</t>
         </is>
       </c>
     </row>
@@ -5835,10 +5902,10 @@
         <v>7.9</v>
       </c>
       <c r="AD30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE30" t="n">
         <v>3</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>4</v>
       </c>
       <c r="AF30" t="n">
         <v>5</v>
@@ -5865,10 +5932,10 @@
         <v>30</v>
       </c>
       <c r="AN30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP30" t="n">
         <v>3</v>
@@ -5907,7 +5974,7 @@
         <v>5</v>
       </c>
       <c r="BB30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC30" t="n">
         <v>3</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>11-29-2007-08</t>
+          <t>2007-11-29</t>
         </is>
       </c>
     </row>
@@ -6017,13 +6084,13 @@
         <v>-0.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG31" t="n">
         <v>17</v>
@@ -6032,7 +6099,7 @@
         <v>4</v>
       </c>
       <c r="AI31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ31" t="n">
         <v>9</v>
@@ -6047,7 +6114,7 @@
         <v>15</v>
       </c>
       <c r="AN31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO31" t="n">
         <v>7</v>
@@ -6056,16 +6123,16 @@
         <v>9</v>
       </c>
       <c r="AQ31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU31" t="n">
         <v>24</v>
@@ -6074,19 +6141,19 @@
         <v>11</v>
       </c>
       <c r="AW31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX31" t="n">
         <v>8</v>
       </c>
       <c r="AY31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ31" t="n">
         <v>13</v>
       </c>
       <c r="BA31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB31" t="n">
         <v>11</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>11-29-2007-08</t>
+          <t>2007-11-29</t>
         </is>
       </c>
     </row>
